--- a/resources/reselling/files/reselling-adv-forecast-gates.xlsx
+++ b/resources/reselling/files/reselling-adv-forecast-gates.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,11 +71,6 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -170,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,8 +209,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -1362,10 +1355,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="20" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B37:D37"/>

--- a/resources/reselling/files/reselling-adv-forecast-gates.xlsx
+++ b/resources/reselling/files/reselling-adv-forecast-gates.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,9 +204,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -577,7 +574,7 @@
   <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -594,8 +591,8 @@
     <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Eight-week forecast + gates + actuals (Reselling — Advanced, ch6, ch9)</t>
         </is>
@@ -608,7 +605,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -657,7 +653,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -725,7 +720,6 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -753,7 +747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Inputs complete?</t>
@@ -764,8 +758,7 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Week</t>
@@ -1266,7 +1259,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -1319,7 +1311,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="33" customHeight="1">
+    <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>VERDICT</t>
@@ -1332,7 +1324,6 @@
       <c r="C37" s="15" t="n"/>
       <c r="D37" s="16" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
@@ -1347,11 +1338,10 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
